--- a/AtchisonRegime/Outputs/India/MSCI_Europe/df_regEquityReturns_MSCI_Europe.xlsx
+++ b/AtchisonRegime/Outputs/India/MSCI_Europe/df_regEquityReturns_MSCI_Europe.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q316"/>
+  <dimension ref="A1:Q317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17857,7 +17857,7 @@
         <v>-1.609197597460336</v>
       </c>
       <c r="C306" t="n">
-        <v>0.1269752971138792</v>
+        <v>-0.1586595595287259</v>
       </c>
       <c r="D306" t="b">
         <v>0</v>
@@ -17914,7 +17914,7 @@
         <v>-1.665486013574585</v>
       </c>
       <c r="C307" t="n">
-        <v>0.08629259774089702</v>
+        <v>0.1383565447898576</v>
       </c>
       <c r="D307" t="b">
         <v>0</v>
@@ -17971,7 +17971,7 @@
         <v>-1.901181816225073</v>
       </c>
       <c r="C308" t="n">
-        <v>0.06631902283450167</v>
+        <v>0.1152177262296182</v>
       </c>
       <c r="D308" t="b">
         <v>0</v>
@@ -18028,7 +18028,7 @@
         <v>-2.093900900681109</v>
       </c>
       <c r="C309" t="n">
-        <v>0.04555869256656515</v>
+        <v>0.09314547075106079</v>
       </c>
       <c r="D309" t="b">
         <v>0</v>
@@ -18085,7 +18085,7 @@
         <v>-1.925045594804248</v>
       </c>
       <c r="C310" t="n">
-        <v>0</v>
+        <v>0.0730366768494552</v>
       </c>
       <c r="D310" t="b">
         <v>0</v>
@@ -18142,7 +18142,7 @@
         <v>-1.272591127701468</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.04929692066057501</v>
+        <v>0.05992091312749612</v>
       </c>
       <c r="D311" t="b">
         <v>0</v>
@@ -18199,13 +18199,13 @@
         <v>-0.8244531695587767</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.05176467051398125</v>
+        <v>0.05405871173099788</v>
       </c>
       <c r="D312" t="b">
         <v>0</v>
       </c>
       <c r="E312" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F312" t="n">
         <v>-1.1038301565745</v>
@@ -18215,22 +18215,22 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Type 3</t>
+          <t>Type 1</t>
         </is>
       </c>
       <c r="J312" t="n">
         <v>0</v>
       </c>
       <c r="K312" t="n">
-        <v>0</v>
+        <v>-1.1038301565745</v>
       </c>
       <c r="L312" t="n">
-        <v>-1.1038301565745</v>
+        <v>0</v>
       </c>
       <c r="M312" t="n">
         <v>0</v>
@@ -18239,10 +18239,10 @@
         <v>148.548465133531</v>
       </c>
       <c r="O312" t="n">
-        <v>311.9523402537453</v>
+        <v>308.5089162478846</v>
       </c>
       <c r="P312" t="n">
-        <v>77.65795079432957</v>
+        <v>78.52473044939887</v>
       </c>
       <c r="Q312" t="n">
         <v>79.35067637407829</v>
@@ -18256,13 +18256,13 @@
         <v>-0.9488965089988395</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.08209071111419658</v>
+        <v>0.05316714534512307</v>
       </c>
       <c r="D313" t="b">
         <v>0</v>
       </c>
       <c r="E313" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F313" t="n">
         <v>2.70141072687946</v>
@@ -18272,22 +18272,22 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>Type 3</t>
+          <t>Type 1</t>
         </is>
       </c>
       <c r="J313" t="n">
         <v>0</v>
       </c>
       <c r="K313" t="n">
-        <v>0</v>
+        <v>2.70141072687946</v>
       </c>
       <c r="L313" t="n">
-        <v>2.70141072687946</v>
+        <v>0</v>
       </c>
       <c r="M313" t="n">
         <v>0</v>
@@ -18296,10 +18296,10 @@
         <v>148.548465133531</v>
       </c>
       <c r="O313" t="n">
-        <v>311.9523402537453</v>
+        <v>316.8430092047846</v>
       </c>
       <c r="P313" t="n">
-        <v>79.75581100736235</v>
+        <v>78.52473044939887</v>
       </c>
       <c r="Q313" t="n">
         <v>79.35067637407829</v>
@@ -18313,13 +18313,13 @@
         <v>-1.209590239554617</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.05812943059160887</v>
+        <v>0.06021053671922057</v>
       </c>
       <c r="D314" t="b">
         <v>0</v>
       </c>
       <c r="E314" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F314" t="n">
         <v>6.12278993736941</v>
@@ -18329,22 +18329,22 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>Type 3</t>
+          <t>Type 1</t>
         </is>
       </c>
       <c r="J314" t="n">
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>0</v>
+        <v>6.12278993736941</v>
       </c>
       <c r="L314" t="n">
-        <v>6.12278993736941</v>
+        <v>0</v>
       </c>
       <c r="M314" t="n">
         <v>0</v>
@@ -18353,10 +18353,10 @@
         <v>148.548465133531</v>
       </c>
       <c r="O314" t="n">
-        <v>311.9523402537453</v>
+        <v>336.2426410896335</v>
       </c>
       <c r="P314" t="n">
-        <v>84.6390917781885</v>
+        <v>78.52473044939887</v>
       </c>
       <c r="Q314" t="n">
         <v>79.35067637407829</v>
@@ -18370,13 +18370,13 @@
         <v>-1.426764933004604</v>
       </c>
       <c r="C315" t="n">
-        <v>-0.09280608837336365</v>
+        <v>0.07188992918729449</v>
       </c>
       <c r="D315" t="b">
         <v>0</v>
       </c>
       <c r="E315" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F315" t="n">
         <v>3.97735373678266</v>
@@ -18386,22 +18386,22 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Type 3</t>
+          <t>Type 1</t>
         </is>
       </c>
       <c r="J315" t="n">
         <v>0</v>
       </c>
       <c r="K315" t="n">
-        <v>0</v>
+        <v>3.97735373678266</v>
       </c>
       <c r="L315" t="n">
-        <v>3.97735373678266</v>
+        <v>0</v>
       </c>
       <c r="M315" t="n">
         <v>0</v>
@@ -18410,10 +18410,10 @@
         <v>148.548465133531</v>
       </c>
       <c r="O315" t="n">
-        <v>311.9523402537453</v>
+        <v>349.6162003396688</v>
       </c>
       <c r="P315" t="n">
-        <v>88.00548785780718</v>
+        <v>78.52473044939887</v>
       </c>
       <c r="Q315" t="n">
         <v>79.35067637407829</v>
@@ -18424,16 +18424,16 @@
         <v>45747</v>
       </c>
       <c r="B316" t="n">
-        <v>-1.542312882396952</v>
+        <v>-1.479076778638796</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.1977619446671215</v>
+        <v>0.08487070723497196</v>
       </c>
       <c r="D316" t="b">
         <v>0</v>
       </c>
       <c r="E316" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F316" t="n">
         <v>1.83191753619591</v>
@@ -18443,22 +18443,22 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>Type 3</t>
+          <t>Type 1</t>
         </is>
       </c>
       <c r="J316" t="n">
         <v>0</v>
       </c>
       <c r="K316" t="n">
-        <v>0</v>
+        <v>1.83191753619591</v>
       </c>
       <c r="L316" t="n">
-        <v>1.83191753619591</v>
+        <v>0</v>
       </c>
       <c r="M316" t="n">
         <v>0</v>
@@ -18467,12 +18467,69 @@
         <v>148.548465133531</v>
       </c>
       <c r="O316" t="n">
-        <v>311.9523402537453</v>
+        <v>356.020880823073</v>
       </c>
       <c r="P316" t="n">
-        <v>89.61767582268912</v>
+        <v>78.52473044939887</v>
       </c>
       <c r="Q316" t="n">
+        <v>79.35067637407829</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B317" t="n">
+        <v>-1.432151479563748</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.09460631327380538</v>
+      </c>
+      <c r="D317" t="b">
+        <v>0</v>
+      </c>
+      <c r="E317" t="b">
+        <v>1</v>
+      </c>
+      <c r="F317" t="n">
+        <v>1.83191753619591</v>
+      </c>
+      <c r="G317" t="n">
+        <v>325618.0893537902</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="J317" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" t="n">
+        <v>1.83191753619591</v>
+      </c>
+      <c r="L317" t="n">
+        <v>0</v>
+      </c>
+      <c r="M317" t="n">
+        <v>0</v>
+      </c>
+      <c r="N317" t="n">
+        <v>148.548465133531</v>
+      </c>
+      <c r="O317" t="n">
+        <v>362.54288977139</v>
+      </c>
+      <c r="P317" t="n">
+        <v>78.52473044939887</v>
+      </c>
+      <c r="Q317" t="n">
         <v>79.35067637407829</v>
       </c>
     </row>
